--- a/it_forms/005_cybersecurity_analyst_exit_survey--it_forms.xlsx
+++ b/it_forms/005_cybersecurity_analyst_exit_survey--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>work_environment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Work Environment</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>tools_used</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Tools Used</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>work_environment</t>
+          <t>processes_used</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>work_environment</t>
+          <t>Processes Used</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>tools</t>
+          <t>job_retention</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tools</t>
+          <t>Job Retention</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>tools</t>
+          <t>process_satisfaction</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>tool_one</t>
+          <t>Process Satisfaction</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>tool_three</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tool_three</t>
+          <t>Suggestions</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>processes</t>
+          <t>tool_frequency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>processes</t>
+          <t>Tool Frequency</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>processes</t>
+          <t>new_tools</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>process_one</t>
+          <t>New Tools</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>processes</t>
+          <t>new_processes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>process_two</t>
+          <t>New Processes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>processes</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>processes</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>processes</t>
+          <t>surprise</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>process_three</t>
+          <t>Surprises or Concerns</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>retention</t>
+          <t>work_environment_changes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>retention</t>
+          <t>Changes in Work Environment</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>retention</t>
+          <t>team_communication</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>retention</t>
+          <t>Team Communication</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,21 +860,67 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>retention</t>
+          <t>favorite_tool</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>retention</t>
+          <t>Favorite Tool</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>least_favorite_tool</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Least Favorite Tool</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>other_comments</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Other Comments</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -891,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -919,238 +965,170 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tools_choices</t>
+          <t>tools_used_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>tool_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tool 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tools_choices</t>
+          <t>tools_used_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>tool_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tool 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tools_choices</t>
+          <t>tools_used_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>tool_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tool 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tools_choices</t>
+          <t>tools_used_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>tool_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tool 4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tool_three_choices</t>
+          <t>processes_used_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>process_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Process 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tool_three_choices</t>
+          <t>processes_used_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>process_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Process 2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>processes_choices</t>
+          <t>processes_used_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>process_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Process 3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>processes_choices</t>
+          <t>processes_used_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>process_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Process 4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>processes_choices</t>
+          <t>job_retention_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>processes_choices</t>
+          <t>job_retention_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>retention_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>retention_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>retention_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>retention_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
